--- a/pregenereated_results/s2/ate_iptw_piecewise_cox_IPTW_Piecewise_Cox_retention.xlsx
+++ b/pregenereated_results/s2/ate_iptw_piecewise_cox_IPTW_Piecewise_Cox_retention.xlsx
@@ -1389,7 +1389,7 @@
         <v>7220</v>
       </c>
       <c r="B2" t="n">
-        <v>7094.386718944054</v>
+        <v>7094.386718944053</v>
       </c>
       <c r="C2" t="n">
         <v>0.9957648995493169</v>
@@ -1404,7 +1404,7 @@
         <v>1.124267686541995</v>
       </c>
       <c r="G2" t="n">
-        <v>1.67804342107184</v>
+        <v>1.678043421071839</v>
       </c>
     </row>
   </sheetData>
@@ -1418,237 +1418,69 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L5"/>
+  <dimension ref="A1:G2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>interval</t>
+          <t>Parameter</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>interval_label</t>
+          <t>Estimate</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>hazard_ratio</t>
+          <t>Std_Error</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>hr_ci_lower</t>
+          <t>CI_Lower</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>hr_ci_upper</t>
+          <t>CI_Upper</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>hr_pvalue</t>
+          <t>P_Value_Raw</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>significant</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>n_at_risk</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>n_events</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>n_events_treated</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>n_events_control</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>concordance</t>
+          <t>Alpha</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>(0, 90)</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>0–3 mo</t>
-        </is>
+          <t>treatment</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>-0.3054678169866643</v>
       </c>
       <c r="C2" t="n">
-        <v>0.5946651297685973</v>
+        <v>0.1304973056123173</v>
       </c>
       <c r="D2" t="n">
-        <v>0.3950448306008492</v>
+        <v>-0.5612425359868061</v>
       </c>
       <c r="E2" t="n">
-        <v>0.8951556612571012</v>
+        <v>-0.0496930979865223</v>
       </c>
       <c r="F2" t="n">
-        <v>0.01274825851729578</v>
-      </c>
-      <c r="G2" t="b">
-        <v>1</v>
-      </c>
-      <c r="H2" t="n">
-        <v>7220</v>
-      </c>
-      <c r="I2" t="n">
-        <v>741</v>
-      </c>
-      <c r="J2" t="n">
-        <v>27</v>
-      </c>
-      <c r="K2" t="n">
-        <v>714</v>
-      </c>
-      <c r="L2" t="n">
-        <v>0.5166682768138802</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>(90, 180)</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>3 mo–6 mo</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
-        <v>0.8448108297088645</v>
-      </c>
-      <c r="D3" t="n">
-        <v>0.4909932659281879</v>
-      </c>
-      <c r="E3" t="n">
-        <v>1.453594962538174</v>
-      </c>
-      <c r="F3" t="n">
-        <v>0.5424758458269043</v>
-      </c>
-      <c r="G3" t="b">
-        <v>0</v>
-      </c>
-      <c r="H3" t="n">
-        <v>6479</v>
-      </c>
-      <c r="I3" t="n">
-        <v>280</v>
-      </c>
-      <c r="J3" t="n">
-        <v>16</v>
-      </c>
-      <c r="K3" t="n">
-        <v>264</v>
-      </c>
-      <c r="L3" t="n">
-        <v>0.5072723389050264</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>(180, 270)</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>6 mo–9 mo</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>0.8985323838340568</v>
-      </c>
-      <c r="D4" t="n">
-        <v>0.4947424068520127</v>
-      </c>
-      <c r="E4" t="n">
-        <v>1.631880416185974</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0.7252729923743723</v>
-      </c>
-      <c r="G4" t="b">
-        <v>0</v>
-      </c>
-      <c r="H4" t="n">
-        <v>6199</v>
-      </c>
-      <c r="I4" t="n">
-        <v>213</v>
-      </c>
-      <c r="J4" t="n">
-        <v>13</v>
-      </c>
-      <c r="K4" t="n">
-        <v>200</v>
-      </c>
-      <c r="L4" t="n">
-        <v>0.5052815720770406</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>(270, 365)</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>9 mo–12 mo</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>0.9438571646370639</v>
-      </c>
-      <c r="D5" t="n">
-        <v>0.5229701823199705</v>
-      </c>
-      <c r="E5" t="n">
-        <v>1.703474456774394</v>
-      </c>
-      <c r="F5" t="n">
-        <v>0.8478999568148919</v>
-      </c>
-      <c r="G5" t="b">
-        <v>0</v>
-      </c>
-      <c r="H5" t="n">
-        <v>5986</v>
-      </c>
-      <c r="I5" t="n">
-        <v>202</v>
-      </c>
-      <c r="J5" t="n">
-        <v>12</v>
-      </c>
-      <c r="K5" t="n">
-        <v>190</v>
-      </c>
-      <c r="L5" t="n">
-        <v>0.5066244166928906</v>
+        <v>0.01924479785888877</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.05</v>
       </c>
     </row>
   </sheetData>
@@ -1694,13 +1526,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>-2.680600179802938</v>
+        <v>-2.68060017980294</v>
       </c>
       <c r="C2" t="n">
-        <v>0.4771933030981325</v>
+        <v>0.4771933030981267</v>
       </c>
       <c r="D2" t="n">
-        <v>1.938181768271168e-08</v>
+        <v>1.93818176827037e-08</v>
       </c>
     </row>
     <row r="3">
@@ -1710,13 +1542,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-0.02542074333516161</v>
+        <v>-0.02542074333516159</v>
       </c>
       <c r="C3" t="n">
-        <v>0.1002143663033997</v>
+        <v>0.1002143663033998</v>
       </c>
       <c r="D3" t="n">
-        <v>0.79975540801217</v>
+        <v>0.7997554080121703</v>
       </c>
     </row>
     <row r="4">
@@ -1726,13 +1558,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.2244463748843409</v>
+        <v>0.2244463748843408</v>
       </c>
       <c r="C4" t="n">
         <v>0.2335027157442914</v>
       </c>
       <c r="D4" t="n">
-        <v>0.3364439424069159</v>
+        <v>0.3364439424069164</v>
       </c>
     </row>
     <row r="5">
@@ -1745,10 +1577,10 @@
         <v>0.8155080917228588</v>
       </c>
       <c r="C5" t="n">
-        <v>0.1734026513921177</v>
+        <v>0.173402651392118</v>
       </c>
       <c r="D5" t="n">
-        <v>2.563995828054277e-06</v>
+        <v>2.563995828054386e-06</v>
       </c>
     </row>
     <row r="6">
@@ -1758,13 +1590,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.03527526670387295</v>
+        <v>0.03527526670387294</v>
       </c>
       <c r="C6" t="n">
-        <v>0.191688294691954</v>
+        <v>0.1916882946919544</v>
       </c>
       <c r="D6" t="n">
-        <v>0.853994545471355</v>
+        <v>0.8539945454713553</v>
       </c>
     </row>
     <row r="7">
@@ -1777,10 +1609,10 @@
         <v>0.2773648159307716</v>
       </c>
       <c r="C7" t="n">
-        <v>0.1901447102133382</v>
+        <v>0.1901447102133385</v>
       </c>
       <c r="D7" t="n">
-        <v>0.1446466431125516</v>
+        <v>0.1446466431125523</v>
       </c>
     </row>
     <row r="8">
@@ -1793,10 +1625,10 @@
         <v>0.1036811851537241</v>
       </c>
       <c r="C8" t="n">
-        <v>0.1952515666982443</v>
+        <v>0.1952515666982444</v>
       </c>
       <c r="D8" t="n">
-        <v>0.5954095400432464</v>
+        <v>0.5954095400432468</v>
       </c>
     </row>
     <row r="9">
@@ -1812,7 +1644,7 @@
         <v>0.1695280942409136</v>
       </c>
       <c r="D9" t="n">
-        <v>2.539495077342701e-07</v>
+        <v>2.539495077342719e-07</v>
       </c>
     </row>
     <row r="10">
@@ -1822,13 +1654,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>-0.04456520772617086</v>
+        <v>-0.04456520772617057</v>
       </c>
       <c r="C10" t="n">
-        <v>0.2604021031716313</v>
+        <v>0.2604021031716314</v>
       </c>
       <c r="D10" t="n">
-        <v>0.8641137091517834</v>
+        <v>0.8641137091517844</v>
       </c>
     </row>
     <row r="11">
@@ -1838,13 +1670,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>-0.2737623724798149</v>
+        <v>-0.2737623724798145</v>
       </c>
       <c r="C11" t="n">
-        <v>0.2787881385465057</v>
+        <v>0.2787881385465063</v>
       </c>
       <c r="D11" t="n">
-        <v>0.3261132423877617</v>
+        <v>0.3261132423877634</v>
       </c>
     </row>
     <row r="12">
@@ -1854,13 +1686,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.08100487957118127</v>
+        <v>0.08100487957118158</v>
       </c>
       <c r="C12" t="n">
-        <v>0.2596429772097166</v>
+        <v>0.2596429772097172</v>
       </c>
       <c r="D12" t="n">
-        <v>0.7550514391424692</v>
+        <v>0.7550514391424689</v>
       </c>
     </row>
     <row r="13">
@@ -1870,13 +1702,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.03917827337461736</v>
+        <v>0.03917827337461771</v>
       </c>
       <c r="C13" t="n">
-        <v>0.2572958805743769</v>
+        <v>0.2572958805743772</v>
       </c>
       <c r="D13" t="n">
-        <v>0.8789745077123745</v>
+        <v>0.8789745077123736</v>
       </c>
     </row>
     <row r="14">
@@ -1886,13 +1718,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>-0.05296103812307947</v>
+        <v>-0.05296103812307912</v>
       </c>
       <c r="C14" t="n">
-        <v>0.2610089865588713</v>
+        <v>0.2610089865588722</v>
       </c>
       <c r="D14" t="n">
-        <v>0.8392062624375523</v>
+        <v>0.8392062624375538</v>
       </c>
     </row>
     <row r="15">
@@ -1902,13 +1734,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.1181322726534159</v>
+        <v>0.1181322726534163</v>
       </c>
       <c r="C15" t="n">
-        <v>0.2572294350577177</v>
+        <v>0.2572294350577189</v>
       </c>
       <c r="D15" t="n">
-        <v>0.646055612898408</v>
+        <v>0.6460556128984085</v>
       </c>
     </row>
     <row r="16">
@@ -1918,13 +1750,13 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>-0.004000986240379581</v>
+        <v>-0.00400098624037939</v>
       </c>
       <c r="C16" t="n">
-        <v>0.2383903410311186</v>
+        <v>0.2383903410311194</v>
       </c>
       <c r="D16" t="n">
-        <v>0.9866094604655129</v>
+        <v>0.9866094604655136</v>
       </c>
     </row>
     <row r="17">
@@ -1934,13 +1766,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.1057185310395304</v>
+        <v>0.1057185310395308</v>
       </c>
       <c r="C17" t="n">
-        <v>0.2543340222421748</v>
+        <v>0.2543340222421757</v>
       </c>
       <c r="D17" t="n">
-        <v>0.6776529122567303</v>
+        <v>0.6776529122567302</v>
       </c>
     </row>
     <row r="18">
@@ -1950,13 +1782,13 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>-0.1377694895733256</v>
+        <v>-0.1377694895733253</v>
       </c>
       <c r="C18" t="n">
-        <v>0.2636874203313626</v>
+        <v>0.2636874203313639</v>
       </c>
       <c r="D18" t="n">
-        <v>0.6013412201546261</v>
+        <v>0.6013412201546287</v>
       </c>
     </row>
     <row r="19">
@@ -1966,13 +1798,13 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>-0.02557154094223238</v>
+        <v>-0.0255715409422322</v>
       </c>
       <c r="C19" t="n">
-        <v>0.252759790153811</v>
+        <v>0.2527597901538112</v>
       </c>
       <c r="D19" t="n">
-        <v>0.9194160355966675</v>
+        <v>0.9194160355966682</v>
       </c>
     </row>
     <row r="20">
@@ -1982,13 +1814,13 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>-0.07344622569376427</v>
+        <v>-0.07344622569376394</v>
       </c>
       <c r="C20" t="n">
-        <v>0.267457860954101</v>
+        <v>0.2674578609541013</v>
       </c>
       <c r="D20" t="n">
-        <v>0.7836169672222772</v>
+        <v>0.7836169672222786</v>
       </c>
     </row>
     <row r="21">
@@ -1998,13 +1830,13 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.2063167170305059</v>
+        <v>0.2063167170305062</v>
       </c>
       <c r="C21" t="n">
-        <v>0.244289653245072</v>
+        <v>0.2442896532450728</v>
       </c>
       <c r="D21" t="n">
-        <v>0.3983578134719846</v>
+        <v>0.3983578134719856</v>
       </c>
     </row>
     <row r="22">
@@ -2014,13 +1846,13 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>-0.1704634573362026</v>
+        <v>-0.1704634573362025</v>
       </c>
       <c r="C22" t="n">
-        <v>0.2696748454965904</v>
+        <v>0.2696748454965907</v>
       </c>
       <c r="D22" t="n">
-        <v>0.5273167196806361</v>
+        <v>0.5273167196806369</v>
       </c>
     </row>
     <row r="23">
@@ -2030,13 +1862,13 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>-0.5008110927334757</v>
+        <v>-0.5008110927334755</v>
       </c>
       <c r="C23" t="n">
-        <v>0.287067218044571</v>
+        <v>0.2870672180445716</v>
       </c>
       <c r="D23" t="n">
-        <v>0.08105838975171785</v>
+        <v>0.08105838975171867</v>
       </c>
     </row>
     <row r="24">
@@ -2046,13 +1878,13 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.9366864721074267</v>
+        <v>0.9366864721074269</v>
       </c>
       <c r="C24" t="n">
         <v>0.1483430409733375</v>
       </c>
       <c r="D24" t="n">
-        <v>2.713396260923891e-10</v>
+        <v>2.713396260923871e-10</v>
       </c>
     </row>
     <row r="25">
@@ -2062,13 +1894,13 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>-0.5776106069409677</v>
+        <v>-0.5776106069409676</v>
       </c>
       <c r="C25" t="n">
-        <v>0.1143619392421807</v>
+        <v>0.1143619392421805</v>
       </c>
       <c r="D25" t="n">
-        <v>4.401383208103943e-07</v>
+        <v>4.401383208103756e-07</v>
       </c>
     </row>
     <row r="26">
@@ -2078,13 +1910,13 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.237316144844174</v>
+        <v>0.2373161448441742</v>
       </c>
       <c r="C26" t="n">
         <v>0.1503781926377478</v>
       </c>
       <c r="D26" t="n">
-        <v>0.1145360411757813</v>
+        <v>0.1145360411757809</v>
       </c>
     </row>
     <row r="27">
@@ -2094,13 +1926,13 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-0.04350476117998651</v>
+        <v>-0.04350476117998649</v>
       </c>
       <c r="C27" t="n">
-        <v>0.1611879340386412</v>
+        <v>0.1611879340386415</v>
       </c>
       <c r="D27" t="n">
-        <v>0.7872365295400213</v>
+        <v>0.7872365295400219</v>
       </c>
     </row>
     <row r="28">
@@ -2110,13 +1942,13 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-0.07514354096975732</v>
+        <v>-0.07514354096975731</v>
       </c>
       <c r="C28" t="n">
         <v>0.1613683918223567</v>
       </c>
       <c r="D28" t="n">
-        <v>0.6414556246120151</v>
+        <v>0.6414556246120153</v>
       </c>
     </row>
     <row r="29">
@@ -2126,93 +1958,93 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.09749293462742097</v>
+        <v>0.09749293462742098</v>
       </c>
       <c r="C29" t="n">
-        <v>0.1543265796290165</v>
+        <v>0.1543265796290168</v>
       </c>
       <c r="D29" t="n">
-        <v>0.5275624553510008</v>
+        <v>0.5275624553510017</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>tenure_months</t>
+          <t>num_direct_reports</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.002418133412192873</v>
+        <v>-0.004129656026475424</v>
       </c>
       <c r="C30" t="n">
-        <v>0.007135781003458546</v>
+        <v>0.02222260881033181</v>
       </c>
       <c r="D30" t="n">
-        <v>0.7347043603418277</v>
+        <v>0.8525770672961283</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>age</t>
+          <t>tot_span_of_control</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.005012017390962195</v>
+        <v>0.006335499136474501</v>
       </c>
       <c r="C31" t="n">
-        <v>0.008304876992455039</v>
+        <v>0.006871422968197188</v>
       </c>
       <c r="D31" t="n">
-        <v>0.5461741835341576</v>
+        <v>0.3565249957666434</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>num_direct_reports</t>
+          <t>age</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.004129656026475419</v>
+        <v>-0.005012017390962181</v>
       </c>
       <c r="C32" t="n">
-        <v>0.02222260881033174</v>
+        <v>0.008304876992454852</v>
       </c>
       <c r="D32" t="n">
-        <v>0.8525770672961279</v>
+        <v>0.5461741835341496</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>is_new_manager</t>
+          <t>tenure_months</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.2280638724458785</v>
+        <v>-0.00241813341219285</v>
       </c>
       <c r="C33" t="n">
-        <v>0.1146565719927948</v>
+        <v>0.007135781003458538</v>
       </c>
       <c r="D33" t="n">
-        <v>0.04668969945129923</v>
+        <v>0.7347043603418298</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>tot_span_of_control</t>
+          <t>is_new_manager</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.006335499136474495</v>
+        <v>0.2280638724458788</v>
       </c>
       <c r="C34" t="n">
-        <v>0.006871422968197181</v>
+        <v>0.1146565719927948</v>
       </c>
       <c r="D34" t="n">
-        <v>0.3565249957666435</v>
+        <v>0.04668969945129902</v>
       </c>
     </row>
   </sheetData>
@@ -2266,13 +2098,13 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.9350702643084896</v>
+        <v>0.9350702643084913</v>
       </c>
       <c r="D2" t="n">
         <v>0.8939763606698742</v>
       </c>
       <c r="E2" t="n">
-        <v>0.04109390363861543</v>
+        <v>0.04109390363861709</v>
       </c>
     </row>
     <row r="3">
@@ -2285,13 +2117,13 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.900193688823673</v>
+        <v>0.9001936888236747</v>
       </c>
       <c r="D3" t="n">
         <v>0.8548025202490657</v>
       </c>
       <c r="E3" t="n">
-        <v>0.04539116857460734</v>
+        <v>0.04539116857460901</v>
       </c>
     </row>
     <row r="4">
@@ -2304,13 +2136,13 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.8720187983946986</v>
+        <v>0.8720187983947002</v>
       </c>
       <c r="D4" t="n">
         <v>0.8250397507431066</v>
       </c>
       <c r="E4" t="n">
-        <v>0.046979047651592</v>
+        <v>0.04697904765159355</v>
       </c>
     </row>
     <row r="5">
@@ -2323,13 +2155,13 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.8436439126637496</v>
+        <v>0.843643912663751</v>
       </c>
       <c r="D5" t="n">
-        <v>0.7967552731684119</v>
+        <v>0.7967552731684091</v>
       </c>
       <c r="E5" t="n">
-        <v>0.04688863949533773</v>
+        <v>0.04688863949534194</v>
       </c>
     </row>
   </sheetData>
